--- a/Test Case/Validazione/10-Lettera Screening/CDA2_Lettera_Screening_OK.xlsx
+++ b/Test Case/Validazione/10-Lettera Screening/CDA2_Lettera_Screening_OK.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29825"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sites.ey.com/sites/IBM-SOGEI-Sogei-FSE2.0-GTW/Shared Documents/Sogei - FSE 2.0 - GTW/02.  Accreditamento - contributo SME per checklist/Validazione/[Accreditamento_Fornitori] - TC OK &amp; KO - 20231213/13-Lettera di Invito per lo Screening/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sites.ey.com/sites/IBM-SOGEI-Sogei-FSE2.0-GTW/Shared Documents/Sogei - FSE 2.0 - GTW/02.  Accreditamento - contributo SME per checklist/Validazione/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2302" documentId="13_ncr:1_{E79C9974-44A8-4BD7-A07F-D25B0F95D955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC38D402-756F-48CD-8269-E2E88C02EAF1}"/>
+  <xr:revisionPtr revIDLastSave="2308" documentId="13_ncr:1_{E79C9974-44A8-4BD7-A07F-D25B0F95D955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1A1059E-8E69-4756-AE0A-047524A03AC3}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{1E8B7D17-95DA-407D-AD12-13C95143136E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{1E8B7D17-95DA-407D-AD12-13C95143136E}"/>
   </bookViews>
   <sheets>
     <sheet name="LEGENDA" sheetId="10" r:id="rId1"/>
@@ -122,6 +122,9 @@
     <t>L'attributo deve essere valorizzato con "COMP".</t>
   </si>
   <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Livello_Screening]</t>
+  </si>
+  <si>
     <t>All'interno della sezione è possibile riportare le informazioni relative all'appuntamento e alle prestazioni previste per lo screening o per gli altri percorsi di prevenzione.</t>
   </si>
   <si>
@@ -131,7 +134,7 @@
     <t>ClinicalDocument/component/structuredBody/component/section[@ID=Livello_Screening]/templateId/@root</t>
   </si>
   <si>
-    <t>L'attributo deve essere valorizzato con "2.16.840.1.113883.3.1937.777.63.10.613".</t>
+    <t>L'attributo deve essere valorizzato con "2.16.840.1.113883.3.1937.777.63.10.941".</t>
   </si>
   <si>
     <t>ClinicalDocument/component/structuredBody/component/section[@ID=Livello_Screening]/id</t>
@@ -161,7 +164,7 @@
     <t>ClinicalDocument/component/structuredBody/component/section[@ID=Livello_Screening]/code/@displayName</t>
   </si>
   <si>
-    <t>L'attributo deve essere valorizzato con "Screening invitation letter".</t>
+    <t>L'attributo deve essere valorizzato con "Screening invitation letter [Text] Narrative Preventive medicine".</t>
   </si>
   <si>
     <t>ClinicalDocument/component/structuredBody/component/section[@ID=Livello_Screening]/title</t>
@@ -482,10 +485,10 @@
     <t>ClinicalDocument/component/structuredBody/component/section[@ID=Livello_Screening]/entry/act/entryRelationship/procedure/code/@displayName</t>
   </si>
   <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_a_invito_precedente]</t>
+  </si>
+  <si>
     <t>Riferimento ad invito precedente</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_a_invito_precedente]</t>
   </si>
   <si>
     <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_a_invito_precedente]/templateId</t>
@@ -685,15 +688,12 @@
   <si>
     <t>2…2</t>
   </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Livello_Screening]</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1206,9 +1206,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1246,7 +1246,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1352,7 +1352,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1494,7 +1494,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1503,14 +1503,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D86993A-F6C8-44BA-A96F-B10B6216C123}">
   <dimension ref="B1:I5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="38.44140625" customWidth="1"/>
-    <col min="9" max="9" width="12.88671875" customWidth="1"/>
+    <col min="2" max="2" width="38.42578125" customWidth="1"/>
+    <col min="9" max="9" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:9" ht="15" thickBot="1"/>
+    <row r="2" spans="2:9">
       <c r="B2" s="14" t="s">
         <v>0</v>
       </c>
@@ -1524,7 +1524,7 @@
       <c r="H2" s="33"/>
       <c r="I2" s="34"/>
     </row>
-    <row r="3" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:9" ht="15" thickBot="1">
       <c r="B3" s="15" t="s">
         <v>2</v>
       </c>
@@ -1538,8 +1538,8 @@
       <c r="H3" s="30"/>
       <c r="I3" s="31"/>
     </row>
-    <row r="4" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="2:9" ht="14.25" customHeight="1"/>
+    <row r="5" spans="2:9" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="C3:I3"/>
@@ -1552,16 +1552,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDBFE66E-2C65-468C-88A7-6E2308A001C0}">
   <dimension ref="A1:G111"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="72.109375" customWidth="1"/>
-    <col min="2" max="3" width="27.33203125" customWidth="1"/>
-    <col min="4" max="5" width="37.44140625" customWidth="1"/>
-    <col min="6" max="6" width="42.5546875" customWidth="1"/>
-    <col min="7" max="7" width="50.6640625" customWidth="1"/>
+    <col min="1" max="1" width="72.140625" customWidth="1"/>
+    <col min="2" max="3" width="27.28515625" customWidth="1"/>
+    <col min="4" max="5" width="37.42578125" customWidth="1"/>
+    <col min="6" max="6" width="42.5703125" customWidth="1"/>
+    <col min="7" max="7" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="41.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="41.45" customHeight="1" thickBot="1">
       <c r="A1" s="8" t="s">
         <v>4</v>
       </c>
@@ -1584,7 +1584,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="43.15" customHeight="1">
       <c r="A2" s="9" t="s">
         <v>11</v>
       </c>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="G2" s="22"/>
     </row>
-    <row r="3" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="43.15" customHeight="1">
       <c r="A3" s="13" t="s">
         <v>15</v>
       </c>
@@ -1626,7 +1626,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="43.15" customHeight="1">
       <c r="A4" s="13" t="s">
         <v>19</v>
       </c>
@@ -1647,7 +1647,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="43.15" customHeight="1">
       <c r="A5" s="5" t="s">
         <v>21</v>
       </c>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="G5" s="23"/>
     </row>
-    <row r="6" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="43.15" customHeight="1">
       <c r="A6" s="13" t="s">
         <v>23</v>
       </c>
@@ -1689,9 +1689,9 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="67.900000000000006" customHeight="1">
       <c r="A7" s="5" t="s">
-        <v>194</v>
+        <v>25</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>12</v>
@@ -1706,13 +1706,13 @@
         <v>13</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G7" s="23"/>
     </row>
-    <row r="8" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="43.15" customHeight="1">
       <c r="A8" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>12</v>
@@ -1729,9 +1729,9 @@
       <c r="F8" s="5"/>
       <c r="G8" s="23"/>
     </row>
-    <row r="9" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="43.15" customHeight="1">
       <c r="A9" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>12</v>
@@ -1747,12 +1747,12 @@
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="23" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="43.15" customHeight="1">
       <c r="A10" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>16</v>
@@ -1769,9 +1769,9 @@
       <c r="F10" s="5"/>
       <c r="G10" s="23"/>
     </row>
-    <row r="11" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="43.15" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>12</v>
@@ -1788,9 +1788,9 @@
       <c r="F11" s="5"/>
       <c r="G11" s="23"/>
     </row>
-    <row r="12" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="43.15" customHeight="1">
       <c r="A12" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>12</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="F12" s="5"/>
       <c r="G12" s="20" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="43.15" customHeight="1">
       <c r="A13" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>12</v>
@@ -1827,12 +1827,12 @@
       </c>
       <c r="F13" s="23"/>
       <c r="G13" s="20" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="43.15" customHeight="1">
       <c r="A14" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>16</v>
@@ -1848,12 +1848,12 @@
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="22" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="43.15" customHeight="1">
       <c r="A15" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>16</v>
@@ -1869,12 +1869,12 @@
       </c>
       <c r="F15" s="5"/>
       <c r="G15" s="23" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="43.15" customHeight="1">
       <c r="A16" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>16</v>
@@ -1890,12 +1890,12 @@
       </c>
       <c r="F16" s="12"/>
       <c r="G16" s="23" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="109.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="109.15" customHeight="1">
       <c r="A17" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>12</v>
@@ -1910,13 +1910,13 @@
         <v>13</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G17" s="23"/>
     </row>
-    <row r="18" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="43.15" customHeight="1">
       <c r="A18" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>16</v>
@@ -1933,9 +1933,9 @@
       <c r="F18" s="5"/>
       <c r="G18" s="23"/>
     </row>
-    <row r="19" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="43.15" customHeight="1">
       <c r="A19" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>12</v>
@@ -1950,13 +1950,13 @@
         <v>13</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G19" s="24"/>
     </row>
-    <row r="20" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="43.15" customHeight="1">
       <c r="A20" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>12</v>
@@ -1972,12 +1972,12 @@
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="23" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="75.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="75.599999999999994" customHeight="1">
       <c r="A21" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>12</v>
@@ -1992,13 +1992,13 @@
         <v>13</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G21" s="24"/>
     </row>
-    <row r="22" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="43.15" customHeight="1">
       <c r="A22" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>16</v>
@@ -2013,13 +2013,13 @@
         <v>13</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G22" s="24"/>
     </row>
-    <row r="23" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="43.15" customHeight="1">
       <c r="A23" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>16</v>
@@ -2035,12 +2035,12 @@
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="24" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="43.15" customHeight="1">
       <c r="A24" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>12</v>
@@ -2057,9 +2057,9 @@
       <c r="F24" s="5"/>
       <c r="G24" s="23"/>
     </row>
-    <row r="25" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="43.15" customHeight="1">
       <c r="A25" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>16</v>
@@ -2075,12 +2075,12 @@
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="23" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="43.15" customHeight="1">
       <c r="A26" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>12</v>
@@ -2097,9 +2097,9 @@
       <c r="F26" s="5"/>
       <c r="G26" s="23"/>
     </row>
-    <row r="27" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="43.15" customHeight="1">
       <c r="A27" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>12</v>
@@ -2116,9 +2116,9 @@
       <c r="F27" s="5"/>
       <c r="G27" s="23"/>
     </row>
-    <row r="28" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="43.15" customHeight="1">
       <c r="A28" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>16</v>
@@ -2135,9 +2135,9 @@
       <c r="F28" s="16"/>
       <c r="G28" s="18"/>
     </row>
-    <row r="29" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="43.15" customHeight="1">
       <c r="A29" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>12</v>
@@ -2152,13 +2152,13 @@
         <v>13</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G29" s="23"/>
     </row>
-    <row r="30" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="43.15" customHeight="1">
       <c r="A30" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>16</v>
@@ -2173,13 +2173,13 @@
         <v>17</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G30" s="23"/>
     </row>
-    <row r="31" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="43.15" customHeight="1">
       <c r="A31" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>16</v>
@@ -2194,13 +2194,13 @@
         <v>17</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G31" s="23"/>
     </row>
-    <row r="32" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="43.15" customHeight="1">
       <c r="A32" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>12</v>
@@ -2215,13 +2215,13 @@
         <v>13</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G32" s="23"/>
     </row>
-    <row r="33" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="43.15" customHeight="1">
       <c r="A33" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>16</v>
@@ -2236,13 +2236,13 @@
         <v>17</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G33" s="23"/>
     </row>
-    <row r="34" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" ht="43.15" customHeight="1">
       <c r="A34" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>12</v>
@@ -2257,13 +2257,13 @@
         <v>13</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G34" s="23"/>
     </row>
-    <row r="35" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" ht="43.15" customHeight="1">
       <c r="A35" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>16</v>
@@ -2278,13 +2278,13 @@
         <v>17</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G35" s="23"/>
     </row>
-    <row r="36" spans="1:7" ht="165.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" ht="165.6" customHeight="1">
       <c r="A36" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>16</v>
@@ -2299,34 +2299,34 @@
         <v>17</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G36" s="23"/>
     </row>
-    <row r="37" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" ht="43.15" customHeight="1">
       <c r="A37" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E37" s="11" t="s">
         <v>17</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G37" s="23"/>
     </row>
-    <row r="38" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" ht="43.15" customHeight="1">
       <c r="A38" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>12</v>
@@ -2343,9 +2343,9 @@
       <c r="F38" s="5"/>
       <c r="G38" s="23"/>
     </row>
-    <row r="39" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" ht="43.15" customHeight="1">
       <c r="A39" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>12</v>
@@ -2362,9 +2362,9 @@
       <c r="F39" s="5"/>
       <c r="G39" s="23"/>
     </row>
-    <row r="40" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="43.15" customHeight="1">
       <c r="A40" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>16</v>
@@ -2381,9 +2381,9 @@
       <c r="F40" s="5"/>
       <c r="G40" s="23"/>
     </row>
-    <row r="41" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" ht="43.15" customHeight="1">
       <c r="A41" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>16</v>
@@ -2398,13 +2398,13 @@
         <v>17</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G41" s="25"/>
     </row>
-    <row r="42" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" ht="43.15" customHeight="1">
       <c r="A42" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>16</v>
@@ -2423,9 +2423,9 @@
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" ht="43.15" customHeight="1">
       <c r="A43" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>12</v>
@@ -2442,9 +2442,9 @@
       <c r="F43" s="5"/>
       <c r="G43" s="23"/>
     </row>
-    <row r="44" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" ht="43.15" customHeight="1">
       <c r="A44" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>16</v>
@@ -2460,12 +2460,12 @@
       </c>
       <c r="F44" s="5"/>
       <c r="G44" s="23" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="43.15" customHeight="1">
       <c r="A45" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>12</v>
@@ -2484,9 +2484,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" ht="43.15" customHeight="1">
       <c r="A46" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>12</v>
@@ -2503,9 +2503,9 @@
       <c r="F46" s="5"/>
       <c r="G46" s="23"/>
     </row>
-    <row r="47" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" ht="43.15" customHeight="1">
       <c r="A47" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>12</v>
@@ -2521,12 +2521,12 @@
       </c>
       <c r="F47" s="5"/>
       <c r="G47" s="26" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="43.15" customHeight="1">
       <c r="A48" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>12</v>
@@ -2542,12 +2542,12 @@
       </c>
       <c r="F48" s="23"/>
       <c r="G48" s="20" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="43.15" customHeight="1">
       <c r="A49" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>16</v>
@@ -2564,9 +2564,9 @@
       <c r="F49" s="5"/>
       <c r="G49" s="22"/>
     </row>
-    <row r="50" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" ht="43.15" customHeight="1">
       <c r="A50" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>16</v>
@@ -2583,9 +2583,9 @@
       <c r="F50" s="5"/>
       <c r="G50" s="23"/>
     </row>
-    <row r="51" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" ht="43.15" customHeight="1">
       <c r="A51" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>16</v>
@@ -2602,9 +2602,9 @@
       <c r="F51" s="5"/>
       <c r="G51" s="23"/>
     </row>
-    <row r="52" spans="1:7" ht="66" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" ht="66" customHeight="1">
       <c r="A52" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>12</v>
@@ -2619,15 +2619,15 @@
         <v>13</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G52" s="23" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="43.15" customHeight="1">
       <c r="A53" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>12</v>
@@ -2642,13 +2642,13 @@
         <v>13</v>
       </c>
       <c r="F53" s="28" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G53" s="23"/>
     </row>
-    <row r="54" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" ht="43.15" customHeight="1">
       <c r="A54" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>12</v>
@@ -2667,9 +2667,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" ht="43.15" customHeight="1">
       <c r="A55" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>12</v>
@@ -2685,12 +2685,12 @@
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="23" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="43.15" customHeight="1">
       <c r="A56" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>16</v>
@@ -2707,9 +2707,9 @@
       <c r="F56" s="5"/>
       <c r="G56" s="26"/>
     </row>
-    <row r="57" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" ht="43.15" customHeight="1">
       <c r="A57" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>16</v>
@@ -2725,12 +2725,12 @@
       </c>
       <c r="F57" s="23"/>
       <c r="G57" s="20" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="43.15" customHeight="1">
       <c r="A58" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>12</v>
@@ -2745,13 +2745,13 @@
         <v>13</v>
       </c>
       <c r="F58" s="17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G58" s="22"/>
     </row>
-    <row r="59" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" ht="72">
       <c r="A59" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>12</v>
@@ -2767,12 +2767,12 @@
       </c>
       <c r="F59" s="5"/>
       <c r="G59" s="23" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="43.15" customHeight="1">
       <c r="A60" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>12</v>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="F60" s="23"/>
       <c r="G60" s="23" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="43.15" customHeight="1">
       <c r="A61" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>16</v>
@@ -2809,12 +2809,12 @@
       </c>
       <c r="F61" s="5"/>
       <c r="G61" s="23" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="72">
       <c r="A62" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>16</v>
@@ -2830,12 +2830,12 @@
       </c>
       <c r="F62" s="5"/>
       <c r="G62" s="23" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="43.15" customHeight="1">
       <c r="A63" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>12</v>
@@ -2850,13 +2850,13 @@
         <v>13</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G63" s="23"/>
     </row>
-    <row r="64" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" ht="43.15" customHeight="1">
       <c r="A64" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>12</v>
@@ -2871,12 +2871,12 @@
         <v>13</v>
       </c>
       <c r="F64" s="28" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="43.15" customHeight="1">
       <c r="A65" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>12</v>
@@ -2895,9 +2895,9 @@
         <v>24</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" ht="62.45" customHeight="1">
       <c r="A66" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>12</v>
@@ -2912,13 +2912,13 @@
         <v>13</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G66" s="23"/>
     </row>
-    <row r="67" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" ht="43.15" customHeight="1">
       <c r="A67" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>16</v>
@@ -2934,12 +2934,12 @@
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="23" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="43.15" customHeight="1">
       <c r="A68" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>16</v>
@@ -2958,9 +2958,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" ht="43.15" customHeight="1">
       <c r="A69" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>16</v>
@@ -2977,9 +2977,9 @@
       <c r="F69" s="5"/>
       <c r="G69" s="26"/>
     </row>
-    <row r="70" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" ht="43.15" customHeight="1">
       <c r="A70" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>16</v>
@@ -2995,12 +2995,12 @@
       </c>
       <c r="F70" s="23"/>
       <c r="G70" s="20" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="43.15" customHeight="1">
       <c r="A71" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>12</v>
@@ -3017,9 +3017,9 @@
       <c r="F71" s="5"/>
       <c r="G71" s="22"/>
     </row>
-    <row r="72" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" ht="43.15" customHeight="1">
       <c r="A72" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>12</v>
@@ -3036,9 +3036,9 @@
       <c r="F72" s="5"/>
       <c r="G72" s="23"/>
     </row>
-    <row r="73" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" ht="43.15" customHeight="1">
       <c r="A73" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>12</v>
@@ -3055,9 +3055,9 @@
       <c r="F73" s="5"/>
       <c r="G73" s="23"/>
     </row>
-    <row r="74" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" ht="43.15" customHeight="1">
       <c r="A74" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>16</v>
@@ -3074,9 +3074,9 @@
       <c r="F74" s="5"/>
       <c r="G74" s="23"/>
     </row>
-    <row r="75" spans="1:7" s="7" customFormat="1" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" s="7" customFormat="1" ht="43.15" customHeight="1">
       <c r="A75" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>16</v>
@@ -3093,7 +3093,7 @@
       <c r="F75" s="5"/>
       <c r="G75" s="23"/>
     </row>
-    <row r="76" spans="1:7" s="7" customFormat="1" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" s="7" customFormat="1" ht="43.15" customHeight="1">
       <c r="A76" s="5" t="s">
         <v>134</v>
       </c>
@@ -3110,13 +3110,13 @@
         <v>17</v>
       </c>
       <c r="F76" s="17" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G76" s="23"/>
     </row>
-    <row r="77" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" ht="43.15" customHeight="1">
       <c r="A77" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>12</v>
@@ -3133,9 +3133,9 @@
       <c r="F77" s="5"/>
       <c r="G77" s="23"/>
     </row>
-    <row r="78" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" ht="43.15" customHeight="1">
       <c r="A78" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>12</v>
@@ -3151,12 +3151,12 @@
       </c>
       <c r="F78" s="5"/>
       <c r="G78" s="23" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="43.15" customHeight="1">
       <c r="A79" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>16</v>
@@ -3173,9 +3173,9 @@
       <c r="F79" s="5"/>
       <c r="G79" s="26"/>
     </row>
-    <row r="80" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" ht="43.15" customHeight="1">
       <c r="A80" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>12</v>
@@ -3192,9 +3192,9 @@
       <c r="F80" s="23"/>
       <c r="G80" s="20"/>
     </row>
-    <row r="81" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" ht="43.15" customHeight="1">
       <c r="A81" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>12</v>
@@ -3210,12 +3210,12 @@
       </c>
       <c r="F81" s="23"/>
       <c r="G81" s="20" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="43.15" customHeight="1">
       <c r="A82" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>12</v>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="F82" s="23"/>
       <c r="G82" s="20" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="43.15" customHeight="1">
       <c r="A83" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>16</v>
@@ -3252,12 +3252,12 @@
       </c>
       <c r="F83" s="23"/>
       <c r="G83" s="20" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="43.15" customHeight="1">
       <c r="A84" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>16</v>
@@ -3273,12 +3273,12 @@
       </c>
       <c r="F84" s="23"/>
       <c r="G84" s="20" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="43.15" customHeight="1">
       <c r="A85" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>16</v>
@@ -3295,9 +3295,9 @@
       <c r="F85" s="5"/>
       <c r="G85" s="22"/>
     </row>
-    <row r="86" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7" ht="43.15" customHeight="1">
       <c r="A86" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>16</v>
@@ -3314,9 +3314,9 @@
       <c r="F86" s="5"/>
       <c r="G86" s="23"/>
     </row>
-    <row r="87" spans="1:7" ht="76.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" ht="76.150000000000006" customHeight="1">
       <c r="A87" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B87" s="5" t="s">
         <v>12</v>
@@ -3331,13 +3331,13 @@
         <v>13</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G87" s="23"/>
     </row>
-    <row r="88" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7" ht="43.15" customHeight="1">
       <c r="A88" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B88" s="5" t="s">
         <v>12</v>
@@ -3354,9 +3354,9 @@
       <c r="F88" s="5"/>
       <c r="G88" s="23"/>
     </row>
-    <row r="89" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" ht="43.15" customHeight="1">
       <c r="A89" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>12</v>
@@ -3372,12 +3372,12 @@
       </c>
       <c r="F89" s="5"/>
       <c r="G89" s="23" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="43.15" customHeight="1">
       <c r="A90" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>12</v>
@@ -3393,12 +3393,12 @@
       </c>
       <c r="F90" s="5"/>
       <c r="G90" s="23" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="43.15" customHeight="1">
       <c r="A91" s="5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>16</v>
@@ -3415,9 +3415,9 @@
       <c r="F91" s="5"/>
       <c r="G91" s="23"/>
     </row>
-    <row r="92" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" ht="43.15" customHeight="1">
       <c r="A92" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>16</v>
@@ -3433,12 +3433,12 @@
       </c>
       <c r="F92" s="5"/>
       <c r="G92" s="23" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="43.15" customHeight="1">
       <c r="A93" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>12</v>
@@ -3455,9 +3455,9 @@
       <c r="F93" s="5"/>
       <c r="G93" s="23"/>
     </row>
-    <row r="94" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" ht="43.15" customHeight="1">
       <c r="A94" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>12</v>
@@ -3473,12 +3473,12 @@
       </c>
       <c r="F94" s="5"/>
       <c r="G94" s="23" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="43.15" customHeight="1">
       <c r="A95" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>12</v>
@@ -3494,12 +3494,12 @@
       </c>
       <c r="F95" s="5"/>
       <c r="G95" s="23" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="43.15" customHeight="1">
       <c r="A96" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>16</v>
@@ -3515,12 +3515,12 @@
       </c>
       <c r="F96" s="5"/>
       <c r="G96" s="23" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="43.15" customHeight="1">
       <c r="A97" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>16</v>
@@ -3536,12 +3536,12 @@
       </c>
       <c r="F97" s="5"/>
       <c r="G97" s="23" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" ht="43.15" customHeight="1">
       <c r="A98" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>12</v>
@@ -3558,9 +3558,9 @@
       <c r="F98" s="5"/>
       <c r="G98" s="23"/>
     </row>
-    <row r="99" spans="1:7" ht="118.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7" ht="118.15" customHeight="1">
       <c r="A99" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>12</v>
@@ -3575,13 +3575,13 @@
         <v>13</v>
       </c>
       <c r="F99" s="12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G99" s="23"/>
     </row>
-    <row r="100" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" ht="43.15" customHeight="1">
       <c r="A100" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>16</v>
@@ -3597,12 +3597,12 @@
       </c>
       <c r="F100" s="5"/>
       <c r="G100" s="23" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="43.15" customHeight="1">
       <c r="A101" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>16</v>
@@ -3621,9 +3621,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="102" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7" ht="43.15" customHeight="1">
       <c r="A102" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>12</v>
@@ -3640,9 +3640,9 @@
       <c r="F102" s="5"/>
       <c r="G102" s="23"/>
     </row>
-    <row r="103" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7" ht="43.15" customHeight="1">
       <c r="A103" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>12</v>
@@ -3659,9 +3659,9 @@
       <c r="F103" s="5"/>
       <c r="G103" s="23"/>
     </row>
-    <row r="104" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" ht="43.15" customHeight="1">
       <c r="A104" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>12</v>
@@ -3678,9 +3678,9 @@
       <c r="F104" s="5"/>
       <c r="G104" s="23"/>
     </row>
-    <row r="105" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7" ht="43.15" customHeight="1">
       <c r="A105" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>16</v>
@@ -3697,9 +3697,9 @@
       <c r="F105" s="5"/>
       <c r="G105" s="23"/>
     </row>
-    <row r="106" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7" ht="43.15" customHeight="1">
       <c r="A106" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B106" s="5" t="s">
         <v>16</v>
@@ -3716,9 +3716,9 @@
       <c r="F106" s="5"/>
       <c r="G106" s="23"/>
     </row>
-    <row r="107" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7" ht="43.15" customHeight="1">
       <c r="A107" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>12</v>
@@ -3735,9 +3735,9 @@
       <c r="F107" s="5"/>
       <c r="G107" s="23"/>
     </row>
-    <row r="108" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7" ht="43.15" customHeight="1">
       <c r="A108" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>12</v>
@@ -3754,9 +3754,9 @@
       <c r="F108" s="5"/>
       <c r="G108" s="23"/>
     </row>
-    <row r="109" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7" ht="43.15" customHeight="1">
       <c r="A109" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>16</v>
@@ -3773,9 +3773,9 @@
       <c r="F109" s="5"/>
       <c r="G109" s="23"/>
     </row>
-    <row r="110" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7" ht="43.15" customHeight="1">
       <c r="A110" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>16</v>
@@ -3792,7 +3792,7 @@
       <c r="F110" s="5"/>
       <c r="G110" s="23"/>
     </row>
-    <row r="111" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="111" spans="1:7" ht="43.15" customHeight="1"/>
   </sheetData>
   <autoFilter ref="A1:G110" xr:uid="{BDBFE66E-2C65-468C-88A7-6E2308A001C0}"/>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -3821,15 +3821,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E87B5470-0087-4830-8706-76B03F96882A}">
   <dimension ref="A1:G110"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="89.6640625" customWidth="1"/>
-    <col min="2" max="3" width="24.5546875" customWidth="1"/>
-    <col min="4" max="5" width="37.33203125" customWidth="1"/>
-    <col min="6" max="7" width="50.6640625" customWidth="1"/>
+    <col min="1" max="1" width="89.7109375" customWidth="1"/>
+    <col min="2" max="3" width="24.5703125" customWidth="1"/>
+    <col min="4" max="5" width="37.28515625" customWidth="1"/>
+    <col min="6" max="7" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="41.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="41.45" customHeight="1" thickBot="1">
       <c r="A1" s="8" t="s">
         <v>4</v>
       </c>
@@ -3840,10 +3840,10 @@
         <v>6</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F1" s="8" t="s">
         <v>9</v>
@@ -3852,7 +3852,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="41.45" customHeight="1">
       <c r="A2" s="9" t="s">
         <v>11</v>
       </c>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="G2" s="22"/>
     </row>
-    <row r="3" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="41.45" customHeight="1">
       <c r="A3" s="9" t="s">
         <v>15</v>
       </c>
@@ -3891,10 +3891,10 @@
       </c>
       <c r="F3" s="9"/>
       <c r="G3" s="22" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="41.45" customHeight="1">
       <c r="A4" s="9" t="s">
         <v>19</v>
       </c>
@@ -3915,7 +3915,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="41.45" customHeight="1">
       <c r="A5" s="5" t="s">
         <v>21</v>
       </c>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="G5" s="23"/>
     </row>
-    <row r="6" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="41.45" customHeight="1">
       <c r="A6" s="9" t="s">
         <v>23</v>
       </c>
@@ -3957,9 +3957,9 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="55.9" customHeight="1">
       <c r="A7" s="5" t="s">
-        <v>194</v>
+        <v>25</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>12</v>
@@ -3974,13 +3974,13 @@
         <v>13</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G7" s="23"/>
     </row>
-    <row r="8" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="41.45" customHeight="1">
       <c r="A8" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>12</v>
@@ -3997,9 +3997,9 @@
       <c r="F8" s="5"/>
       <c r="G8" s="23"/>
     </row>
-    <row r="9" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="41.45" customHeight="1">
       <c r="A9" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>12</v>
@@ -4015,12 +4015,12 @@
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="23" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="41.45" customHeight="1">
       <c r="A10" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>16</v>
@@ -4037,9 +4037,9 @@
       <c r="F10" s="5"/>
       <c r="G10" s="23"/>
     </row>
-    <row r="11" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="41.45" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>12</v>
@@ -4056,9 +4056,9 @@
       <c r="F11" s="5"/>
       <c r="G11" s="26"/>
     </row>
-    <row r="12" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="41.45" customHeight="1">
       <c r="A12" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>12</v>
@@ -4074,12 +4074,12 @@
       </c>
       <c r="F12" s="23"/>
       <c r="G12" s="27" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="41.45" customHeight="1">
       <c r="A13" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>12</v>
@@ -4095,12 +4095,12 @@
       </c>
       <c r="F13" s="23"/>
       <c r="G13" s="20" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="41.45" customHeight="1">
       <c r="A14" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>16</v>
@@ -4116,12 +4116,12 @@
       </c>
       <c r="F14" s="23"/>
       <c r="G14" s="20" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="41.45" customHeight="1">
       <c r="A15" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>16</v>
@@ -4137,12 +4137,12 @@
       </c>
       <c r="F15" s="23"/>
       <c r="G15" s="20" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="41.45" customHeight="1">
       <c r="A16" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>16</v>
@@ -4159,9 +4159,9 @@
       <c r="F16" s="12"/>
       <c r="G16" s="22"/>
     </row>
-    <row r="17" spans="1:7" ht="112.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="112.9" customHeight="1">
       <c r="A17" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>12</v>
@@ -4176,13 +4176,13 @@
         <v>13</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G17" s="23"/>
     </row>
-    <row r="18" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="41.45" customHeight="1">
       <c r="A18" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>16</v>
@@ -4199,9 +4199,9 @@
       <c r="F18" s="5"/>
       <c r="G18" s="23"/>
     </row>
-    <row r="19" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="41.45" customHeight="1">
       <c r="A19" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>12</v>
@@ -4216,13 +4216,13 @@
         <v>13</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G19" s="24"/>
     </row>
-    <row r="20" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="41.45" customHeight="1">
       <c r="A20" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>12</v>
@@ -4238,12 +4238,12 @@
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="23" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="81" customHeight="1" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="81" customHeight="1">
       <c r="A21" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>12</v>
@@ -4258,13 +4258,13 @@
         <v>13</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G21" s="24"/>
     </row>
-    <row r="22" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="41.45" customHeight="1">
       <c r="A22" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>16</v>
@@ -4279,13 +4279,13 @@
         <v>13</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G22" s="24"/>
     </row>
-    <row r="23" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="41.45" customHeight="1">
       <c r="A23" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>16</v>
@@ -4301,12 +4301,12 @@
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="24" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="41.45" customHeight="1">
       <c r="A24" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>16</v>
@@ -4323,9 +4323,9 @@
       <c r="F24" s="5"/>
       <c r="G24" s="23"/>
     </row>
-    <row r="25" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="41.45" customHeight="1">
       <c r="A25" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>16</v>
@@ -4341,12 +4341,12 @@
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="23" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="41.45" customHeight="1">
       <c r="A26" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>16</v>
@@ -4363,9 +4363,9 @@
       <c r="F26" s="5"/>
       <c r="G26" s="23"/>
     </row>
-    <row r="27" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="41.45" customHeight="1">
       <c r="A27" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>12</v>
@@ -4382,9 +4382,9 @@
       <c r="F27" s="5"/>
       <c r="G27" s="23"/>
     </row>
-    <row r="28" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="41.45" customHeight="1">
       <c r="A28" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>16</v>
@@ -4401,9 +4401,9 @@
       <c r="F28" s="5"/>
       <c r="G28" s="23"/>
     </row>
-    <row r="29" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="41.45" customHeight="1">
       <c r="A29" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>12</v>
@@ -4418,13 +4418,13 @@
         <v>13</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G29" s="23"/>
     </row>
-    <row r="30" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="41.45" customHeight="1">
       <c r="A30" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>16</v>
@@ -4439,13 +4439,13 @@
         <v>17</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G30" s="23"/>
     </row>
-    <row r="31" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="41.45" customHeight="1">
       <c r="A31" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>16</v>
@@ -4460,13 +4460,13 @@
         <v>17</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G31" s="23"/>
     </row>
-    <row r="32" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="41.45" customHeight="1">
       <c r="A32" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>12</v>
@@ -4481,13 +4481,13 @@
         <v>13</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G32" s="23"/>
     </row>
-    <row r="33" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="41.45" customHeight="1">
       <c r="A33" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>16</v>
@@ -4502,13 +4502,13 @@
         <v>17</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G33" s="23"/>
     </row>
-    <row r="34" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" ht="41.45" customHeight="1">
       <c r="A34" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>12</v>
@@ -4523,13 +4523,13 @@
         <v>13</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G34" s="23"/>
     </row>
-    <row r="35" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" ht="41.45" customHeight="1">
       <c r="A35" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>16</v>
@@ -4544,13 +4544,13 @@
         <v>17</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G35" s="23"/>
     </row>
-    <row r="36" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" ht="41.45" customHeight="1">
       <c r="A36" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>16</v>
@@ -4565,34 +4565,34 @@
         <v>17</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G36" s="23"/>
     </row>
-    <row r="37" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" ht="41.45" customHeight="1">
       <c r="A37" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>13</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G37" s="23"/>
     </row>
-    <row r="38" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" ht="41.45" customHeight="1">
       <c r="A38" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>12</v>
@@ -4609,9 +4609,9 @@
       <c r="F38" s="5"/>
       <c r="G38" s="23"/>
     </row>
-    <row r="39" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" ht="41.45" customHeight="1">
       <c r="A39" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>12</v>
@@ -4628,9 +4628,9 @@
       <c r="F39" s="5"/>
       <c r="G39" s="23"/>
     </row>
-    <row r="40" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="41.45" customHeight="1">
       <c r="A40" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>16</v>
@@ -4647,9 +4647,9 @@
       <c r="F40" s="5"/>
       <c r="G40" s="23"/>
     </row>
-    <row r="41" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" ht="41.45" customHeight="1">
       <c r="A41" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>16</v>
@@ -4664,13 +4664,13 @@
         <v>13</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G41" s="25"/>
     </row>
-    <row r="42" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" ht="41.45" customHeight="1">
       <c r="A42" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>16</v>
@@ -4689,9 +4689,9 @@
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" ht="41.45" customHeight="1">
       <c r="A43" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>12</v>
@@ -4708,9 +4708,9 @@
       <c r="F43" s="5"/>
       <c r="G43" s="23"/>
     </row>
-    <row r="44" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" ht="41.45" customHeight="1">
       <c r="A44" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>16</v>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="F44" s="5"/>
       <c r="G44" s="23" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="41.45" customHeight="1">
       <c r="A45" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>12</v>
@@ -4750,9 +4750,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" ht="41.45" customHeight="1">
       <c r="A46" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>12</v>
@@ -4769,9 +4769,9 @@
       <c r="F46" s="5"/>
       <c r="G46" s="23"/>
     </row>
-    <row r="47" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" ht="41.45" customHeight="1">
       <c r="A47" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>12</v>
@@ -4787,12 +4787,12 @@
       </c>
       <c r="F47" s="5"/>
       <c r="G47" s="23" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="41.45" customHeight="1">
       <c r="A48" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>12</v>
@@ -4808,12 +4808,12 @@
       </c>
       <c r="F48" s="5"/>
       <c r="G48" s="23" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="41.45" customHeight="1">
       <c r="A49" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>16</v>
@@ -4829,12 +4829,12 @@
       </c>
       <c r="F49" s="5"/>
       <c r="G49" s="23" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="41.45" customHeight="1">
       <c r="A50" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>16</v>
@@ -4851,9 +4851,9 @@
       <c r="F50" s="5"/>
       <c r="G50" s="23"/>
     </row>
-    <row r="51" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" ht="41.45" customHeight="1">
       <c r="A51" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>16</v>
@@ -4870,9 +4870,9 @@
       <c r="F51" s="5"/>
       <c r="G51" s="23"/>
     </row>
-    <row r="52" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" ht="41.45" customHeight="1">
       <c r="A52" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>12</v>
@@ -4887,15 +4887,15 @@
         <v>13</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G52" s="23" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="43.15" customHeight="1">
       <c r="A53" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>12</v>
@@ -4911,12 +4911,12 @@
       </c>
       <c r="F53" s="5"/>
       <c r="G53" s="23" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="41.45" customHeight="1">
       <c r="A54" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>12</v>
@@ -4935,9 +4935,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" ht="41.45" customHeight="1">
       <c r="A55" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>12</v>
@@ -4953,12 +4953,12 @@
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="23" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="41.45" customHeight="1">
       <c r="A56" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>16</v>
@@ -4975,9 +4975,9 @@
       <c r="F56" s="5"/>
       <c r="G56" s="23"/>
     </row>
-    <row r="57" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" ht="41.45" customHeight="1">
       <c r="A57" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>16</v>
@@ -4993,12 +4993,12 @@
       </c>
       <c r="F57" s="5"/>
       <c r="G57" s="23" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="41.45" customHeight="1">
       <c r="A58" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>12</v>
@@ -5013,13 +5013,13 @@
         <v>13</v>
       </c>
       <c r="F58" s="17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G58" s="23"/>
     </row>
-    <row r="59" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" ht="72">
       <c r="A59" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>12</v>
@@ -5035,12 +5035,12 @@
       </c>
       <c r="F59" s="5"/>
       <c r="G59" s="23" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="41.45" customHeight="1">
       <c r="A60" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>12</v>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="F60" s="5"/>
       <c r="G60" s="23" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="41.45" customHeight="1">
       <c r="A61" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>16</v>
@@ -5077,12 +5077,12 @@
       </c>
       <c r="F61" s="5"/>
       <c r="G61" s="23" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="72">
       <c r="A62" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>16</v>
@@ -5098,12 +5098,12 @@
       </c>
       <c r="F62" s="5"/>
       <c r="G62" s="23" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="41.45" customHeight="1">
       <c r="A63" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>12</v>
@@ -5118,13 +5118,13 @@
         <v>13</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G63" s="23"/>
     </row>
-    <row r="64" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" ht="41.45" customHeight="1">
       <c r="A64" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>12</v>
@@ -5139,12 +5139,12 @@
         <v>13</v>
       </c>
       <c r="F64" s="28" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="41.45" customHeight="1">
       <c r="A65" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>12</v>
@@ -5163,9 +5163,9 @@
         <v>24</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" ht="57.6">
       <c r="A66" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>12</v>
@@ -5180,13 +5180,13 @@
         <v>13</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G66" s="23"/>
     </row>
-    <row r="67" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" ht="41.45" customHeight="1">
       <c r="A67" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>16</v>
@@ -5202,12 +5202,12 @@
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="23" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="41.45" customHeight="1">
       <c r="A68" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>16</v>
@@ -5226,9 +5226,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" ht="41.45" customHeight="1">
       <c r="A69" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>16</v>
@@ -5245,9 +5245,9 @@
       <c r="F69" s="5"/>
       <c r="G69" s="26"/>
     </row>
-    <row r="70" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" ht="41.45" customHeight="1">
       <c r="A70" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>16</v>
@@ -5263,12 +5263,12 @@
       </c>
       <c r="F70" s="23"/>
       <c r="G70" s="20" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="41.45" customHeight="1">
       <c r="A71" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>12</v>
@@ -5285,9 +5285,9 @@
       <c r="F71" s="5"/>
       <c r="G71" s="22"/>
     </row>
-    <row r="72" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" ht="41.45" customHeight="1">
       <c r="A72" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>12</v>
@@ -5304,9 +5304,9 @@
       <c r="F72" s="5"/>
       <c r="G72" s="23"/>
     </row>
-    <row r="73" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" ht="41.45" customHeight="1">
       <c r="A73" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>12</v>
@@ -5323,9 +5323,9 @@
       <c r="F73" s="5"/>
       <c r="G73" s="23"/>
     </row>
-    <row r="74" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" ht="41.45" customHeight="1">
       <c r="A74" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>16</v>
@@ -5342,9 +5342,9 @@
       <c r="F74" s="5"/>
       <c r="G74" s="23"/>
     </row>
-    <row r="75" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" ht="41.45" customHeight="1">
       <c r="A75" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>16</v>
@@ -5361,7 +5361,7 @@
       <c r="F75" s="5"/>
       <c r="G75" s="23"/>
     </row>
-    <row r="76" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" ht="41.45" customHeight="1">
       <c r="A76" s="5" t="s">
         <v>134</v>
       </c>
@@ -5378,13 +5378,13 @@
         <v>13</v>
       </c>
       <c r="F76" s="17" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G76" s="23"/>
     </row>
-    <row r="77" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" ht="41.45" customHeight="1">
       <c r="A77" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>12</v>
@@ -5401,9 +5401,9 @@
       <c r="F77" s="5"/>
       <c r="G77" s="26"/>
     </row>
-    <row r="78" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" ht="41.45" customHeight="1">
       <c r="A78" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>12</v>
@@ -5419,12 +5419,12 @@
       </c>
       <c r="F78" s="23"/>
       <c r="G78" s="20" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="41.45" customHeight="1">
       <c r="A79" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>16</v>
@@ -5441,9 +5441,9 @@
       <c r="F79" s="5"/>
       <c r="G79" s="22"/>
     </row>
-    <row r="80" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" ht="41.45" customHeight="1">
       <c r="A80" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>12</v>
@@ -5460,9 +5460,9 @@
       <c r="F80" s="5"/>
       <c r="G80" s="23"/>
     </row>
-    <row r="81" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" ht="41.45" customHeight="1">
       <c r="A81" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>12</v>
@@ -5478,12 +5478,12 @@
       </c>
       <c r="F81" s="5"/>
       <c r="G81" s="23" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="41.45" customHeight="1">
       <c r="A82" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>12</v>
@@ -5499,12 +5499,12 @@
       </c>
       <c r="F82" s="5"/>
       <c r="G82" s="23" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="41.45" customHeight="1">
       <c r="A83" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>16</v>
@@ -5520,12 +5520,12 @@
       </c>
       <c r="F83" s="5"/>
       <c r="G83" s="23" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="41.45" customHeight="1">
       <c r="A84" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>16</v>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="F84" s="5"/>
       <c r="G84" s="23" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="41.45" customHeight="1">
       <c r="A85" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>16</v>
@@ -5563,9 +5563,9 @@
       <c r="F85" s="5"/>
       <c r="G85" s="23"/>
     </row>
-    <row r="86" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7" ht="41.45" customHeight="1">
       <c r="A86" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>16</v>
@@ -5582,9 +5582,9 @@
       <c r="F86" s="5"/>
       <c r="G86" s="23"/>
     </row>
-    <row r="87" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" ht="41.45" customHeight="1">
       <c r="A87" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B87" s="5" t="s">
         <v>12</v>
@@ -5599,13 +5599,13 @@
         <v>13</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G87" s="23"/>
     </row>
-    <row r="88" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7" ht="41.45" customHeight="1">
       <c r="A88" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B88" s="5" t="s">
         <v>12</v>
@@ -5622,9 +5622,9 @@
       <c r="F88" s="5"/>
       <c r="G88" s="23"/>
     </row>
-    <row r="89" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" ht="41.45" customHeight="1">
       <c r="A89" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>12</v>
@@ -5643,9 +5643,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" ht="41.45" customHeight="1">
       <c r="A90" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>12</v>
@@ -5661,12 +5661,12 @@
       </c>
       <c r="F90" s="5"/>
       <c r="G90" s="23" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="41.45" customHeight="1">
       <c r="A91" s="5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>16</v>
@@ -5683,9 +5683,9 @@
       <c r="F91" s="5"/>
       <c r="G91" s="26"/>
     </row>
-    <row r="92" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" ht="41.45" customHeight="1">
       <c r="A92" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>16</v>
@@ -5701,12 +5701,12 @@
       </c>
       <c r="F92" s="23"/>
       <c r="G92" s="27" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="41.45" customHeight="1">
       <c r="A93" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>12</v>
@@ -5723,9 +5723,9 @@
       <c r="F93" s="5"/>
       <c r="G93" s="22"/>
     </row>
-    <row r="94" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" ht="41.45" customHeight="1">
       <c r="A94" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>12</v>
@@ -5741,12 +5741,12 @@
       </c>
       <c r="F94" s="5"/>
       <c r="G94" s="23" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="41.45" customHeight="1">
       <c r="A95" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>12</v>
@@ -5762,12 +5762,12 @@
       </c>
       <c r="F95" s="5"/>
       <c r="G95" s="23" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="41.45" customHeight="1">
       <c r="A96" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>16</v>
@@ -5783,12 +5783,12 @@
       </c>
       <c r="F96" s="5"/>
       <c r="G96" s="23" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="41.45" customHeight="1">
       <c r="A97" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>16</v>
@@ -5804,12 +5804,12 @@
       </c>
       <c r="F97" s="5"/>
       <c r="G97" s="23" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" ht="41.45" customHeight="1">
       <c r="A98" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>12</v>
@@ -5826,9 +5826,9 @@
       <c r="F98" s="5"/>
       <c r="G98" s="23"/>
     </row>
-    <row r="99" spans="1:7" ht="97.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7" ht="97.9" customHeight="1">
       <c r="A99" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>12</v>
@@ -5843,13 +5843,13 @@
         <v>13</v>
       </c>
       <c r="F99" s="12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G99" s="23"/>
     </row>
-    <row r="100" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" ht="41.45" customHeight="1">
       <c r="A100" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>16</v>
@@ -5865,12 +5865,12 @@
       </c>
       <c r="F100" s="5"/>
       <c r="G100" s="23" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="41.45" customHeight="1">
       <c r="A101" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>16</v>
@@ -5889,9 +5889,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="102" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7" ht="41.45" customHeight="1">
       <c r="A102" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>12</v>
@@ -5908,9 +5908,9 @@
       <c r="F102" s="5"/>
       <c r="G102" s="23"/>
     </row>
-    <row r="103" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7" ht="41.45" customHeight="1">
       <c r="A103" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>12</v>
@@ -5927,9 +5927,9 @@
       <c r="F103" s="5"/>
       <c r="G103" s="23"/>
     </row>
-    <row r="104" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" ht="41.45" customHeight="1">
       <c r="A104" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>12</v>
@@ -5946,9 +5946,9 @@
       <c r="F104" s="5"/>
       <c r="G104" s="23"/>
     </row>
-    <row r="105" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7" ht="41.45" customHeight="1">
       <c r="A105" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>16</v>
@@ -5965,9 +5965,9 @@
       <c r="F105" s="5"/>
       <c r="G105" s="26"/>
     </row>
-    <row r="106" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7" ht="41.45" customHeight="1">
       <c r="A106" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B106" s="5" t="s">
         <v>16</v>
@@ -5984,9 +5984,9 @@
       <c r="F106" s="18"/>
       <c r="G106" s="21"/>
     </row>
-    <row r="107" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7" ht="41.45" customHeight="1">
       <c r="A107" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>12</v>
@@ -6003,9 +6003,9 @@
       <c r="F107" s="5"/>
       <c r="G107" s="22"/>
     </row>
-    <row r="108" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7" ht="41.45" customHeight="1">
       <c r="A108" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>12</v>
@@ -6022,9 +6022,9 @@
       <c r="F108" s="5"/>
       <c r="G108" s="23"/>
     </row>
-    <row r="109" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7" ht="41.45" customHeight="1">
       <c r="A109" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>16</v>
@@ -6041,9 +6041,9 @@
       <c r="F109" s="5"/>
       <c r="G109" s="23"/>
     </row>
-    <row r="110" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7" ht="41.45" customHeight="1">
       <c r="A110" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>16</v>
@@ -6092,74 +6092,74 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0DB0DB4-9D32-4E11-8F2F-DBB39CFC572F}">
   <dimension ref="B2:B15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:2">
       <c r="B2" s="3" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.3">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2">
       <c r="B3" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:2">
       <c r="B4" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:2">
       <c r="B6" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.3">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2">
       <c r="B7" s="1" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.3">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2">
       <c r="B8" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:2">
       <c r="B9" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2">
       <c r="B10" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:2">
       <c r="B11" s="1" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="12" spans="2:2" x14ac:dyDescent="0.3">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2">
       <c r="B12" s="4" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="13" spans="2:2" x14ac:dyDescent="0.3">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2">
       <c r="B13" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="14" spans="2:2" x14ac:dyDescent="0.3">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2">
       <c r="B14" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="15" spans="2:2" x14ac:dyDescent="0.3">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2">
       <c r="B15" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -6170,20 +6170,19 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3d04b37e-0497-498c-96f6-8855740e5edb">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010099D50BAF6148C0469FC2106F96A8440B" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0ded3a6aadbdf34d96c7fc30e5856767">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3d04b37e-0497-498c-96f6-8855740e5edb" xmlns:ns3="14722739-9480-433a-8c7c-4ec5d8a77ba5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f351b1b6c8daa9a12afc7a7c24e3e10f" ns2:_="" ns3:_="">
-    <xsd:import namespace="3d04b37e-0497-498c-96f6-8855740e5edb"/>
-    <xsd:import namespace="14722739-9480-433a-8c7c-4ec5d8a77ba5"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A92AB09DCDF6014AA0D6826BF29E2C8E" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="58b13f75919cba2dcad85f84b1d5db00">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1e76d14e-d0ce-457c-8343-9b55836d9ead" xmlns:ns3="a56712a3-8dfd-4688-917a-22f0cf513b89" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3b16ea44285e6579c272a3325f660d0" ns2:_="" ns3:_="">
+    <xsd:import namespace="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
+    <xsd:import namespace="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -6192,16 +6191,22 @@
               <xsd:all>
                 <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
                 <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:UserStoryALM" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -6209,7 +6214,7 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3d04b37e-0497-498c-96f6-8855740e5edb" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="1e76d14e-d0ce-457c-8343-9b55836d9ead" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
@@ -6222,55 +6227,96 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="10" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="11" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+    <xsd:element name="MediaServiceOCR" ma:index="11" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
       <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="33ef62f9-2e07-484b-bd79-00aec90129fe" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="15" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="16" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="18" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="6d165d17-9b79-46c3-82b9-c927e733c429" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
         </xsd:sequence>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+    <xsd:element name="MediaLengthInSeconds" ma:index="23" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
       <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
+        <xsd:restriction base="dms:Unknown"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="17" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+    <xsd:element name="MediaServiceSearchProperties" ma:index="24" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
       <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="18" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+    <xsd:element name="UserStoryALM" ma:index="25" nillable="true" ma:displayName="UserStory ALM" ma:format="Dropdown" ma:internalName="UserStoryALM">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Choice">
+          <xsd:enumeration value="137048 - Stesura checklist RAP"/>
+          <xsd:enumeration value="137049 - Sviluppo testcase RAP"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="26" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="14722739-9480-433a-8c7c-4ec5d8a77ba5" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="a56712a3-8dfd-4688-917a-22f0cf513b89" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="TaxCatchAll" ma:index="19" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{c488629b-a647-4465-8bb2-a216a95770f0}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="a56712a3-8dfd-4688-917a-22f0cf513b89">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithUsers" ma:index="20" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -6289,7 +6335,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="21" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -6397,54 +6443,25 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
+    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{99C0AEB7-C55A-461D-A0CE-4337A3223303}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="14722739-9480-433a-8c7c-4ec5d8a77ba5"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="3d04b37e-0497-498c-96f6-8855740e5edb"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F51A983D-5463-4E4A-8B75-1C405A420DB2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E5885C3-EF55-4CB5-87D1-3C703588E643}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="3d04b37e-0497-498c-96f6-8855740e5edb"/>
-    <ds:schemaRef ds:uri="14722739-9480-433a-8c7c-4ec5d8a77ba5"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C27CE4FA-F25D-46A3-A414-A6F7CD8B5C39}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F51A983D-5463-4E4A-8B75-1C405A420DB2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{99C0AEB7-C55A-461D-A0CE-4337A3223303}"/>
 </file>